--- a/data/trending_integrated_20261020_12.xlsx
+++ b/data/trending_integrated_20261020_12.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77200</v>
+        <v>76100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.69%</t>
+          <t>'+17.98%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -584,7 +584,7 @@
         <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H2" t="n">
         <v>5.95</v>
@@ -610,7 +610,7 @@
         <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>111311182150</v>
+        <v>116733868100</v>
       </c>
       <c r="P2" t="n">
         <v>148300</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10240</v>
+        <v>10360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.28%</t>
+          <t>'+13.60%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.86</v>
       </c>
       <c r="E3" t="n">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="F3" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G3" t="n">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>189573589845</v>
+        <v>191920262945</v>
       </c>
       <c r="P3" t="n">
         <v>11250</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇 및 ESS 사업의 강점과 수주잔고에 대한 긍정적 전망.</t>
+          <t>로봇 관련주로서의 강세 전망과 함께 신고가 경신, 조단위 시총 기대감이 언급된다. 임원 매수 및 ESS, 이차전지 사업과의 연관성이 긍정적으로 평가된다.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['ESS', '로봇']</t>
+          <t>['로봇주', '신고가', 'ESS']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,18 +751,18 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3835</v>
+        <v>3880</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.27%</t>
+          <t>'+3.47%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
@@ -794,7 +794,7 @@
         <v>1.66</v>
       </c>
       <c r="O4" t="n">
-        <v>38167319337</v>
+        <v>38509127440</v>
       </c>
       <c r="P4" t="n">
         <v>6660</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19970</v>
+        <v>20000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.32%</t>
+          <t>'+1.47%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.25</v>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H5" t="n">
         <v>3.07</v>
@@ -886,7 +886,7 @@
         <v>3.32</v>
       </c>
       <c r="O5" t="n">
-        <v>83901178340</v>
+        <v>84273739700</v>
       </c>
       <c r="P5" t="n">
         <v>22450</v>
@@ -949,10 +949,10 @@
         <v>145</v>
       </c>
       <c r="F6" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G6" t="n">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="H6" t="n">
         <v>13.11</v>
@@ -978,7 +978,7 @@
         <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>10296714475</v>
+        <v>10424590925</v>
       </c>
       <c r="P6" t="n">
         <v>69200</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>215000</v>
+        <v>214750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.38%</t>
+          <t>'-1.49%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G7" t="n">
-        <v>1380</v>
+        <v>1372</v>
       </c>
       <c r="H7" t="n">
         <v>46.04</v>
@@ -1070,7 +1070,7 @@
         <v>45.99</v>
       </c>
       <c r="O7" t="n">
-        <v>1470444721500</v>
+        <v>1500742830500</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 부정적 언급이 다수.</t>
+          <t>정치적 이슈와 관련된 부정적 언급이 주를 이루며, 투자 심리에 대한 우려가 나타난다. 금감원의 공매도 중단 논의 및 연기금 매도세에 대한 언급이 있다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['공매도', '연기금', '정치']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7330</v>
+        <v>7310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.74%</t>
+          <t>'-2.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F8" t="n">
         <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>8739799630</v>
+        <v>8851242040</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1244000</v>
+        <v>1234000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.58%</t>
+          <t>'-3.37%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G9" t="n">
-        <v>1572</v>
+        <v>1623</v>
       </c>
       <c r="H9" t="n">
         <v>48.81</v>
@@ -1254,7 +1254,7 @@
         <v>48.82</v>
       </c>
       <c r="O9" t="n">
-        <v>2405851039500</v>
+        <v>2456078109000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>솔리다임 상장 관련 불확실성 및 정치적 이슈 언급.</t>
+          <t>솔리다임 상장 철회 요구와 함께 경영진에 대한 불만이 제기된다. 전반적으로 주가 하락 및 시장 상황에 대한 부정적 인식이 지배적이다.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['솔리다임']</t>
+          <t>['솔리다임', '최태원', '주가 하락']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14495</v>
+        <v>14430</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.04%</t>
+          <t>'-3.48%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F10" t="n">
         <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H10" t="n">
         <v>9.779999999999999</v>
@@ -1346,7 +1346,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>16008802100</v>
+        <v>16234258860</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,21 +1395,21 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17640</v>
+        <v>17600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-3.83%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G11" t="n">
         <v>145</v>
@@ -1438,7 +1438,7 @@
         <v>27.85</v>
       </c>
       <c r="O11" t="n">
-        <v>28248302395</v>
+        <v>28643051150</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2575</v>
+        <v>2570</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.45%</t>
+          <t>'-4.64%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H12" t="n">
         <v>1.14</v>
@@ -1530,7 +1530,7 @@
         <v>0.8</v>
       </c>
       <c r="O12" t="n">
-        <v>27966965761</v>
+        <v>28104244096</v>
       </c>
       <c r="P12" t="n">
         <v>2755</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31500</v>
+        <v>31400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-7.22%</t>
+          <t>'-7.51%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H13" t="n">
         <v>12.79</v>
@@ -1622,7 +1622,7 @@
         <v>12.81</v>
       </c>
       <c r="O13" t="n">
-        <v>45633684725</v>
+        <v>47083293025</v>
       </c>
       <c r="P13" t="n">
         <v>59300</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1603</v>
+        <v>1613</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-8.30%</t>
+          <t>'-7.72%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>83</v>
       </c>
       <c r="G14" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H14" t="n">
         <v>1.77</v>
@@ -1714,7 +1714,7 @@
         <v>0.83</v>
       </c>
       <c r="O14" t="n">
-        <v>67602640358</v>
+        <v>67838367074</v>
       </c>
       <c r="P14" t="n">
         <v>2970</v>
@@ -1759,171 +1759,171 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8680</v>
+        <v>7950</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-10.70%</t>
+          <t>'-11.07%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.15</v>
+        <v>-0.38</v>
       </c>
       <c r="E15" t="n">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
-        <v>232</v>
+        <v>118</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>36.01</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>9720</v>
+        <v>8940</v>
       </c>
       <c r="K15" t="n">
-        <v>9930</v>
+        <v>9000</v>
       </c>
       <c r="L15" t="n">
-        <v>9930</v>
+        <v>9010</v>
       </c>
       <c r="M15" t="n">
-        <v>8630</v>
+        <v>7750</v>
       </c>
       <c r="N15" t="n">
-        <v>6.15</v>
+        <v>36.39</v>
       </c>
       <c r="O15" t="n">
-        <v>14440046470</v>
+        <v>16211149210</v>
       </c>
       <c r="P15" t="n">
-        <v>14940</v>
+        <v>19150</v>
       </c>
       <c r="Q15" t="n">
-        <v>5390</v>
+        <v>3570</v>
       </c>
       <c r="R15" t="n">
-        <v>-273000</v>
+        <v>-36000</v>
       </c>
       <c r="S15" t="n">
-        <v>-244000</v>
+        <v>-8000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 하락 및 개인 투자자들의 어려움에 대한 언급.</t>
+          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['테슬라']</t>
+          <t>['실적', '유상증자', 'RCPS']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>033790</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7970</v>
+        <v>72650</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.85%</t>
+          <t>'-11.40%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.38</v>
+        <v>-0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>59</v>
+        <v>190</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="G16" t="n">
-        <v>108</v>
+        <v>629</v>
       </c>
       <c r="H16" t="n">
-        <v>36.01</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8940</v>
+        <v>82000</v>
       </c>
       <c r="K16" t="n">
-        <v>9000</v>
+        <v>79400</v>
       </c>
       <c r="L16" t="n">
-        <v>9010</v>
+        <v>79400</v>
       </c>
       <c r="M16" t="n">
-        <v>7750</v>
+        <v>70300</v>
       </c>
       <c r="N16" t="n">
-        <v>36.39</v>
+        <v>9.44</v>
       </c>
       <c r="O16" t="n">
-        <v>16042809880</v>
+        <v>86715837300</v>
       </c>
       <c r="P16" t="n">
-        <v>19150</v>
+        <v>184000</v>
       </c>
       <c r="Q16" t="n">
-        <v>3570</v>
+        <v>44750</v>
       </c>
       <c r="R16" t="n">
-        <v>-36000</v>
+        <v>-480000</v>
       </c>
       <c r="S16" t="n">
-        <v>-8000</v>
+        <v>-49000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
+          <t>공매도에 대한 강한 불만과 함께 주가 하락의 이유를 찾기 어렵다는 의견이 제기된다. 금감원 신고 등 적극적인 대응을 주장하는 목소리도 있다.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적', '유상증자', 'RCPS']</t>
+          <t>['공매도', '주가 하락', '금감원']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,43 +1931,43 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>72800</v>
+        <v>8610</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-11.22%</t>
+          <t>'-11.42%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.06</v>
+        <v>-0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>188</v>
+        <v>111</v>
       </c>
       <c r="F17" t="n">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="G17" t="n">
-        <v>620</v>
+        <v>249</v>
       </c>
       <c r="H17" t="n">
-        <v>9.380000000000001</v>
+        <v>6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>82000</v>
+        <v>9720</v>
       </c>
       <c r="K17" t="n">
-        <v>79400</v>
+        <v>9930</v>
       </c>
       <c r="L17" t="n">
-        <v>79400</v>
+        <v>9930</v>
       </c>
       <c r="M17" t="n">
-        <v>70300</v>
+        <v>8610</v>
       </c>
       <c r="N17" t="n">
-        <v>9.44</v>
+        <v>6.15</v>
       </c>
       <c r="O17" t="n">
-        <v>85245555000</v>
+        <v>14755379175</v>
       </c>
       <c r="P17" t="n">
-        <v>184000</v>
+        <v>14940</v>
       </c>
       <c r="Q17" t="n">
-        <v>44750</v>
+        <v>5390</v>
       </c>
       <c r="R17" t="n">
-        <v>-480000</v>
+        <v>-273000</v>
       </c>
       <c r="S17" t="n">
-        <v>-49000</v>
+        <v>-244000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>공매도 관련 불만 및 정치적 이슈에 대한 부정적 언급.</t>
+          <t>주가 급등락에 대한 의구심과 함께 매매 동향에 대한 언급이 있다. 공매도와 개인 투자자들의 움직임에 주목하며, 주가 하락에 대한 우려가 나타난다.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공매도', '방산']</t>
+          <t>['급등락', '매매 동향', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>009900</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261020_12.xlsx
+++ b/data/trending_integrated_20261020_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76100</v>
+        <v>75300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.98%</t>
+          <t>'+16.74%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.29</v>
       </c>
       <c r="E2" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="H2" t="n">
         <v>5.95</v>
@@ -610,7 +610,7 @@
         <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>116733868100</v>
+        <v>120059291850</v>
       </c>
       <c r="P2" t="n">
         <v>148300</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10360</v>
+        <v>10290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.60%</t>
+          <t>'+12.83%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.86</v>
       </c>
       <c r="E3" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F3" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G3" t="n">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>191920262945</v>
+        <v>194645692175</v>
       </c>
       <c r="P3" t="n">
         <v>11250</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇 관련주로서의 강세 전망과 함께 신고가 경신, 조단위 시총 기대감이 언급된다. 임원 매수 및 ESS, 이차전지 사업과의 연관성이 긍정적으로 평가된다.</t>
+          <t>ESS, 로봇, 이차전지 관련주로 폭등 중이며, 신고가 돌파 및 조단위 시총 기대감 형성. 임원 매수 및 메가트렌드 내러티브.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇주', '신고가', 'ESS']</t>
+          <t>['로봇', 'ESS', '메가트렌드']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3880</v>
+        <v>3865</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.47%</t>
+          <t>'+3.07%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,7 +765,7 @@
         <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
         <v>23</v>
@@ -794,7 +794,7 @@
         <v>1.66</v>
       </c>
       <c r="O4" t="n">
-        <v>38509127440</v>
+        <v>38706388386</v>
       </c>
       <c r="P4" t="n">
         <v>6660</v>
@@ -854,10 +854,10 @@
         <v>-0.25</v>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
         <v>128</v>
@@ -886,7 +886,7 @@
         <v>3.32</v>
       </c>
       <c r="O5" t="n">
-        <v>84273739700</v>
+        <v>84524861420</v>
       </c>
       <c r="P5" t="n">
         <v>22450</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42650</v>
+        <v>42600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.70%</t>
+          <t>'-0.81%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>145</v>
       </c>
       <c r="F6" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G6" t="n">
-        <v>846</v>
+        <v>860</v>
       </c>
       <c r="H6" t="n">
         <v>13.11</v>
@@ -978,7 +978,7 @@
         <v>13.04</v>
       </c>
       <c r="O6" t="n">
-        <v>10424590925</v>
+        <v>10563717475</v>
       </c>
       <c r="P6" t="n">
         <v>69200</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>C1 발표 및 FDA 승인 관련 기대감이 있으나, 주가 상승 여부에 대한 불확실성 및 시장 신뢰 회복 필요성 등 언급.</t>
+          <t>C1 발표 및 담관암 FDA 승인 기대감 속에서도 관망세 유지. 주포의 매수세 및 신뢰 회복 필요성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['C1', 'FDA 승인', '담관암']</t>
+          <t>['C1', 'FDA승인', '담관암']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>214750</v>
+        <v>214000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.49%</t>
+          <t>'-1.83%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G7" t="n">
-        <v>1372</v>
+        <v>1410</v>
       </c>
       <c r="H7" t="n">
         <v>46.04</v>
@@ -1070,7 +1070,7 @@
         <v>45.99</v>
       </c>
       <c r="O7" t="n">
-        <v>1500742830500</v>
+        <v>1521627483750</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 부정적 언급이 주를 이루며, 투자 심리에 대한 우려가 나타난다. 금감원의 공매도 중단 논의 및 연기금 매도세에 대한 언급이 있다.</t>
+          <t>정치적 이슈와 맞물린 부정적 시장 전망 및 개인 투자자들의 불만 고조. 실질적 투자 근거는 미흡.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공매도', '연기금', '정치']</t>
+          <t>['정치', '시장전망', '투자']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7310</v>
+        <v>7280</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.01%</t>
+          <t>'-2.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F8" t="n">
         <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>8851242040</v>
+        <v>9005410370</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1234000</v>
+        <v>1230000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.37%</t>
+          <t>'-3.68%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="G9" t="n">
-        <v>1623</v>
+        <v>1642</v>
       </c>
       <c r="H9" t="n">
         <v>48.81</v>
@@ -1254,7 +1254,7 @@
         <v>48.82</v>
       </c>
       <c r="O9" t="n">
-        <v>2456078109000</v>
+        <v>2501931591500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 요구와 함께 경영진에 대한 불만이 제기된다. 전반적으로 주가 하락 및 시장 상황에 대한 부정적 인식이 지배적이다.</t>
+          <t>솔리다임 상장 철회 요구 및 정치적 이슈와 연관된 부정적 여론 형성. 개인 투자자들의 매수 자제 권고.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['솔리다임', '최태원', '주가 하락']</t>
+          <t>['솔리다임', '상장철회', '정치']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14430</v>
+        <v>14380</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.48%</t>
+          <t>'-3.81%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H10" t="n">
         <v>9.779999999999999</v>
@@ -1346,7 +1346,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>16234258860</v>
+        <v>16442814910</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>3분기 실적 폭증 기대에도 불구하고 주가 하락. 주가 조작 및 공매도 관련 의혹 제기.</t>
+          <t>실적 개선에도 불구하고 정치적 이슈와 공매도 관련 불만 고조. 주주들의 대차 해지 독려 및 시장 신뢰 하락.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '주가조작']</t>
+          <t>['실적', '공매도', '대차해지']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17600</v>
+        <v>17560</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.83%</t>
+          <t>'-4.04%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H11" t="n">
         <v>27.78</v>
@@ -1438,7 +1438,7 @@
         <v>27.85</v>
       </c>
       <c r="O11" t="n">
-        <v>28643051150</v>
+        <v>29358509285</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2570</v>
+        <v>2560</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.64%</t>
+          <t>'-5.01%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H12" t="n">
         <v>1.14</v>
@@ -1530,7 +1530,7 @@
         <v>0.8</v>
       </c>
       <c r="O12" t="n">
-        <v>28104244096</v>
+        <v>28255641776</v>
       </c>
       <c r="P12" t="n">
         <v>2755</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31400</v>
+        <v>31350</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-7.51%</t>
+          <t>'-7.66%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H13" t="n">
         <v>12.79</v>
@@ -1622,7 +1622,7 @@
         <v>12.81</v>
       </c>
       <c r="O13" t="n">
-        <v>47083293025</v>
+        <v>48407433950</v>
       </c>
       <c r="P13" t="n">
         <v>59300</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1613</v>
+        <v>1594</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-7.72%</t>
+          <t>'-8.81%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F14" t="n">
         <v>83</v>
       </c>
       <c r="G14" t="n">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="H14" t="n">
         <v>1.77</v>
@@ -1714,7 +1714,7 @@
         <v>0.83</v>
       </c>
       <c r="O14" t="n">
-        <v>67838367074</v>
+        <v>68229877135</v>
       </c>
       <c r="P14" t="n">
         <v>2970</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시로 인한 급등세 기록. 3일간 코스피 수익률 3위 달성.</t>
+          <t>스페이스X 관련 호재 공시 및 기술력 입증으로 인한 강한 상승 기대감 형성. 2연상 이상 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재', '급등']</t>
+          <t>['스페이스X', '호재공시', '강관']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,171 +1759,171 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7950</v>
+        <v>8590</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-11.07%</t>
+          <t>'-11.63%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="E15" t="n">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>118</v>
+        <v>261</v>
       </c>
       <c r="H15" t="n">
-        <v>36.01</v>
+        <v>6</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8940</v>
+        <v>9720</v>
       </c>
       <c r="K15" t="n">
-        <v>9000</v>
+        <v>9930</v>
       </c>
       <c r="L15" t="n">
-        <v>9010</v>
+        <v>9930</v>
       </c>
       <c r="M15" t="n">
-        <v>7750</v>
+        <v>8550</v>
       </c>
       <c r="N15" t="n">
-        <v>36.39</v>
+        <v>6.15</v>
       </c>
       <c r="O15" t="n">
-        <v>16211149210</v>
+        <v>15157412555</v>
       </c>
       <c r="P15" t="n">
-        <v>19150</v>
+        <v>14940</v>
       </c>
       <c r="Q15" t="n">
-        <v>3570</v>
+        <v>5390</v>
       </c>
       <c r="R15" t="n">
-        <v>-36000</v>
+        <v>-273000</v>
       </c>
       <c r="S15" t="n">
-        <v>-8000</v>
+        <v>-244000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
+          <t>주주환원 미흡 및 중복 상장 우려 제기로 인한 주가 하락세 지속. 개인 투자자들의 불만 및 매도 압력.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['실적', '유상증자', 'RCPS']</t>
+          <t>['주주환원', '중복상장', '매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>72650</v>
+        <v>7900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-11.40%</t>
+          <t>'-11.63%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.06</v>
+        <v>-0.38</v>
       </c>
       <c r="E16" t="n">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="F16" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>629</v>
+        <v>124</v>
       </c>
       <c r="H16" t="n">
-        <v>9.380000000000001</v>
+        <v>36.01</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>82000</v>
+        <v>8940</v>
       </c>
       <c r="K16" t="n">
-        <v>79400</v>
+        <v>9000</v>
       </c>
       <c r="L16" t="n">
-        <v>79400</v>
+        <v>9010</v>
       </c>
       <c r="M16" t="n">
-        <v>70300</v>
+        <v>7750</v>
       </c>
       <c r="N16" t="n">
-        <v>9.44</v>
+        <v>36.39</v>
       </c>
       <c r="O16" t="n">
-        <v>86715837300</v>
+        <v>16497682170</v>
       </c>
       <c r="P16" t="n">
-        <v>184000</v>
+        <v>19150</v>
       </c>
       <c r="Q16" t="n">
-        <v>44750</v>
+        <v>3570</v>
       </c>
       <c r="R16" t="n">
-        <v>-480000</v>
+        <v>-36000</v>
       </c>
       <c r="S16" t="n">
-        <v>-49000</v>
+        <v>-8000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>공매도에 대한 강한 불만과 함께 주가 하락의 이유를 찾기 어렵다는 의견이 제기된다. 금감원 신고 등 적극적인 대응을 주장하는 목소리도 있다.</t>
+          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도', '주가 하락', '금감원']</t>
+          <t>['실적', '유상증자', 'RCPS']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,43 +1931,43 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>033790</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8610</v>
+        <v>72300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-11.42%</t>
+          <t>'-11.83%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>111</v>
+        <v>195</v>
       </c>
       <c r="F17" t="n">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="G17" t="n">
-        <v>249</v>
+        <v>645</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>9720</v>
+        <v>82000</v>
       </c>
       <c r="K17" t="n">
-        <v>9930</v>
+        <v>79400</v>
       </c>
       <c r="L17" t="n">
-        <v>9930</v>
+        <v>79400</v>
       </c>
       <c r="M17" t="n">
-        <v>8610</v>
+        <v>70300</v>
       </c>
       <c r="N17" t="n">
-        <v>6.15</v>
+        <v>9.44</v>
       </c>
       <c r="O17" t="n">
-        <v>14755379175</v>
+        <v>88472035650</v>
       </c>
       <c r="P17" t="n">
-        <v>14940</v>
+        <v>184000</v>
       </c>
       <c r="Q17" t="n">
-        <v>5390</v>
+        <v>44750</v>
       </c>
       <c r="R17" t="n">
-        <v>-273000</v>
+        <v>-480000</v>
       </c>
       <c r="S17" t="n">
-        <v>-244000</v>
+        <v>-49000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 급등락에 대한 의구심과 함께 매매 동향에 대한 언급이 있다. 공매도와 개인 투자자들의 움직임에 주목하며, 주가 하락에 대한 우려가 나타난다.</t>
+          <t>공매도에 대한 강한 불만과 함께 주가 하락의 이유를 찾기 어렵다는 의견이 제기된다. 금감원 신고 등 적극적인 대응을 주장하는 목소리도 있다.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['급등락', '매매 동향', '공매도']</t>
+          <t>['공매도', '주가 하락', '금감원']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>272210</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261020_12.xlsx
+++ b/data/trending_integrated_20261020_12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75300</v>
+        <v>75100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.74%</t>
+          <t>'+16.43%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.29</v>
       </c>
       <c r="E2" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F2" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="H2" t="n">
         <v>5.95</v>
@@ -610,7 +610,7 @@
         <v>5.66</v>
       </c>
       <c r="O2" t="n">
-        <v>120059291850</v>
+        <v>124691125150</v>
       </c>
       <c r="P2" t="n">
         <v>148300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>반도체 소부장 섹터 내에서 강세 보이며 지수 대비 높은 등락률 기록.</t>
+          <t>반도체 업황 개선 및 소캠 매출 기대로 인한 상승세 전망. 일부 투자자는 고점 및 폭락 가능성 경고.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['반도체', '소부장', '강세']</t>
+          <t>['반도체', '소캠 매출', '고점 경고']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,7 +643,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10290</v>
+        <v>10370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.83%</t>
+          <t>'+13.71%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.86</v>
       </c>
       <c r="E3" t="n">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="F3" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="G3" t="n">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>194645692175</v>
+        <v>207416055965</v>
       </c>
       <c r="P3" t="n">
         <v>11250</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ESS, 로봇, 이차전지 관련주로 폭등 중이며, 신고가 돌파 및 조단위 시총 기대감 형성. 임원 매수 및 메가트렌드 내러티브.</t>
+          <t>로봇, ESS, 이차전지 테마 연계 및 신고가 경신에 따른 급등 기대감. 조단위 시총 및 5배 이상 상승 가능성 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇', 'ESS', '메가트렌드']</t>
+          <t>['로봇 테마', '신고가', '조단위 시총']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,18 +751,18 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3865</v>
+        <v>3945</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.07%</t>
+          <t>'+5.20%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
         <v>28</v>
@@ -794,7 +794,7 @@
         <v>1.66</v>
       </c>
       <c r="O4" t="n">
-        <v>38706388386</v>
+        <v>40799352254</v>
       </c>
       <c r="P4" t="n">
         <v>6660</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20000</v>
+        <v>17040</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.47%</t>
+          <t>'+5.19%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.25</v>
+        <v>0.96</v>
       </c>
       <c r="E5" t="n">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G5" t="n">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="H5" t="n">
-        <v>3.07</v>
+        <v>2.03</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>19710</v>
+        <v>16200</v>
       </c>
       <c r="K5" t="n">
-        <v>19450</v>
+        <v>16500</v>
       </c>
       <c r="L5" t="n">
-        <v>21850</v>
+        <v>18620</v>
       </c>
       <c r="M5" t="n">
-        <v>19450</v>
+        <v>14650</v>
       </c>
       <c r="N5" t="n">
-        <v>3.32</v>
+        <v>1.07</v>
       </c>
       <c r="O5" t="n">
-        <v>84524861420</v>
+        <v>49282000160</v>
       </c>
       <c r="P5" t="n">
-        <v>22450</v>
+        <v>62100</v>
       </c>
       <c r="Q5" t="n">
-        <v>6320</v>
+        <v>14600</v>
       </c>
       <c r="R5" t="n">
-        <v>-4000</v>
+        <v>-2000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>로봇 섹터와 연관 기대감 및 보안주로서의 역할 언급. 주가 변동성 및 개인 투자자 이탈에 대한 우려.</t>
+          <t>보호예수 물량 출회 및 빅웨이브와의 주가 차이에 대한 불만 제기. 근거 없는 급등락 반복에 대한 비판.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,51 +911,51 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안주', '로봇', '변동성']</t>
+          <t>['보호예수', '주가 차이', '근거 부재']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42600</v>
+        <v>19790</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.81%</t>
+          <t>'+0.41%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.25</v>
       </c>
       <c r="E6" t="n">
-        <v>145</v>
+        <v>77</v>
       </c>
       <c r="F6" t="n">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>860</v>
+        <v>133</v>
       </c>
       <c r="H6" t="n">
-        <v>13.11</v>
+        <v>3.07</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,143 +963,143 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>42950</v>
+        <v>19710</v>
       </c>
       <c r="K6" t="n">
-        <v>42600</v>
+        <v>19450</v>
       </c>
       <c r="L6" t="n">
-        <v>43200</v>
+        <v>21850</v>
       </c>
       <c r="M6" t="n">
-        <v>41550</v>
+        <v>19450</v>
       </c>
       <c r="N6" t="n">
-        <v>13.04</v>
+        <v>3.32</v>
       </c>
       <c r="O6" t="n">
-        <v>10563717475</v>
+        <v>86506667670</v>
       </c>
       <c r="P6" t="n">
-        <v>69200</v>
+        <v>22450</v>
       </c>
       <c r="Q6" t="n">
-        <v>24150</v>
+        <v>6320</v>
       </c>
       <c r="R6" t="n">
-        <v>-21000</v>
+        <v>-4000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>C1 발표 및 담관암 FDA 승인 기대감 속에서도 관망세 유지. 주포의 매수세 및 신뢰 회복 필요성 언급.</t>
+          <t>로봇 섹터와 연관 기대감 및 보안주로서의 역할 언급. 주가 변동성 및 개인 투자자 이탈에 대한 우려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['C1', 'FDA승인', '담관암']</t>
+          <t>['보안주', '로봇', '변동성']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>214000</v>
+        <v>42750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.83%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>152</v>
       </c>
       <c r="F7" t="n">
-        <v>508</v>
+        <v>95</v>
       </c>
       <c r="G7" t="n">
-        <v>1410</v>
+        <v>885</v>
       </c>
       <c r="H7" t="n">
-        <v>46.04</v>
+        <v>13.11</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>218000</v>
+        <v>42950</v>
       </c>
       <c r="K7" t="n">
-        <v>219500</v>
+        <v>42600</v>
       </c>
       <c r="L7" t="n">
-        <v>219500</v>
+        <v>43200</v>
       </c>
       <c r="M7" t="n">
-        <v>210000</v>
+        <v>41550</v>
       </c>
       <c r="N7" t="n">
-        <v>45.99</v>
+        <v>13.04</v>
       </c>
       <c r="O7" t="n">
-        <v>1521627483750</v>
+        <v>11193222750</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>69200</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>24150</v>
       </c>
       <c r="R7" t="n">
-        <v>356000</v>
+        <v>-21000</v>
       </c>
       <c r="S7" t="n">
-        <v>-501000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물린 부정적 시장 전망 및 개인 투자자들의 불만 고조. 실질적 투자 근거는 미흡.</t>
+          <t>C1 발표 임박 및 FDA 승인 이슈 기반 상승 기대감 존재. 하지만 발표 지연 및 주가 부진으로 인한 불안감 혼재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['정치', '시장전망', '투자']</t>
+          <t>['C1 발표', 'FDA 승인', '불안감']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7280</v>
+        <v>7290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.41%</t>
+          <t>'-2.28%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="H8" t="n">
         <v>25.4</v>
@@ -1162,7 +1162,7 @@
         <v>25.42</v>
       </c>
       <c r="O8" t="n">
-        <v>9005410370</v>
+        <v>9522513180</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1230000</v>
+        <v>211500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.68%</t>
+          <t>'-2.98%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="G9" t="n">
-        <v>1642</v>
+        <v>1531</v>
       </c>
       <c r="H9" t="n">
-        <v>48.81</v>
+        <v>46.04</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1277000</v>
+        <v>218000</v>
       </c>
       <c r="K9" t="n">
-        <v>1265000</v>
+        <v>219500</v>
       </c>
       <c r="L9" t="n">
-        <v>1267000</v>
+        <v>219500</v>
       </c>
       <c r="M9" t="n">
-        <v>1183000</v>
+        <v>210000</v>
       </c>
       <c r="N9" t="n">
-        <v>48.82</v>
+        <v>45.99</v>
       </c>
       <c r="O9" t="n">
-        <v>2501931591500</v>
+        <v>1675664590000</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>465500</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>-204000</v>
+        <v>356000</v>
       </c>
       <c r="S9" t="n">
-        <v>-146000</v>
+        <v>-501000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 요구 및 정치적 이슈와 연관된 부정적 여론 형성. 개인 투자자들의 매수 자제 권고.</t>
+          <t>이재명 대표 관련 정치적 논쟁 및 정부 정책 비판이 주를 이룸. 주가 관련 구체적인 분석이나 근거는 부재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['솔리다임', '상장철회', '정치']</t>
+          <t>['정치 논쟁', '정부 정책', '이재명']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14380</v>
+        <v>1224000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.81%</t>
+          <t>'-4.15%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>536</v>
       </c>
       <c r="G10" t="n">
-        <v>142</v>
+        <v>1528</v>
       </c>
       <c r="H10" t="n">
-        <v>9.779999999999999</v>
+        <v>48.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14950</v>
+        <v>1277000</v>
       </c>
       <c r="K10" t="n">
-        <v>14610</v>
+        <v>1265000</v>
       </c>
       <c r="L10" t="n">
-        <v>14940</v>
+        <v>1267000</v>
       </c>
       <c r="M10" t="n">
-        <v>14150</v>
+        <v>1183000</v>
       </c>
       <c r="N10" t="n">
-        <v>9.699999999999999</v>
+        <v>48.82</v>
       </c>
       <c r="O10" t="n">
-        <v>16442814910</v>
+        <v>2661778569000</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>465500</v>
       </c>
       <c r="R10" t="n">
-        <v>-56000</v>
+        <v>-204000</v>
       </c>
       <c r="S10" t="n">
-        <v>-39000</v>
+        <v>-146000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>실적 개선에도 불구하고 정치적 이슈와 공매도 관련 불만 고조. 주주들의 대차 해지 독려 및 시장 신뢰 하락.</t>
+          <t>자회사 솔리다임 우회상장 반대 청원 및 이재명 대표 관련 정치적 발언이 주를 이룸. 주가 하락에 대한 책임 전가 양상.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '대차해지']</t>
+          <t>['솔리다임', '우회상장', '정치 논쟁']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17560</v>
+        <v>14310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.04%</t>
+          <t>'-4.28%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H11" t="n">
-        <v>27.78</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18300</v>
+        <v>14950</v>
       </c>
       <c r="K11" t="n">
-        <v>18140</v>
+        <v>14610</v>
       </c>
       <c r="L11" t="n">
-        <v>18140</v>
+        <v>14940</v>
       </c>
       <c r="M11" t="n">
-        <v>17280</v>
+        <v>14150</v>
       </c>
       <c r="N11" t="n">
-        <v>27.85</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>29358509285</v>
+        <v>17251611435</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>17210</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-247000</v>
+        <v>-56000</v>
       </c>
       <c r="S11" t="n">
-        <v>-134000</v>
+        <v>-39000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
+          <t>실적 개선에도 불구하고 정치적 이슈와 공매도 관련 불만 고조. 주주들의 대차 해지 독려 및 시장 신뢰 하락.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
+          <t>['실적', '공매도', '대차해지']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2560</v>
+        <v>17430</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.01%</t>
+          <t>'-4.75%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.34</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="H12" t="n">
-        <v>1.14</v>
+        <v>27.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2695</v>
+        <v>18300</v>
       </c>
       <c r="K12" t="n">
-        <v>2645</v>
+        <v>18140</v>
       </c>
       <c r="L12" t="n">
-        <v>2715</v>
+        <v>18140</v>
       </c>
       <c r="M12" t="n">
-        <v>2510</v>
+        <v>17280</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8</v>
+        <v>27.85</v>
       </c>
       <c r="O12" t="n">
-        <v>28255641776</v>
+        <v>31555831570</v>
       </c>
       <c r="P12" t="n">
-        <v>2755</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>865</v>
+        <v>17210</v>
       </c>
       <c r="R12" t="n">
-        <v>-12000</v>
+        <v>-247000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-134000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 법인 하이브리드 부품 수주(1000억 규모) 및 역대급 3분기 실적 발표. 주가 상승 기대.</t>
+          <t>조선업 부진 및 반도체 관련 종목 동반 하락 우려 속에서 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['하이브리드 부품', '수주', '실적']</t>
+          <t>['조선업 부진', '반도체 하락', '주가 하락']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31350</v>
+        <v>2545</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-7.66%</t>
+          <t>'-5.57%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.02</v>
+        <v>0.34</v>
       </c>
       <c r="E13" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="H13" t="n">
-        <v>12.79</v>
+        <v>1.14</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>33950</v>
+        <v>2695</v>
       </c>
       <c r="K13" t="n">
-        <v>33250</v>
+        <v>2645</v>
       </c>
       <c r="L13" t="n">
-        <v>34150</v>
+        <v>2715</v>
       </c>
       <c r="M13" t="n">
-        <v>31300</v>
+        <v>2510</v>
       </c>
       <c r="N13" t="n">
-        <v>12.81</v>
+        <v>0.8</v>
       </c>
       <c r="O13" t="n">
-        <v>48407433950</v>
+        <v>29089768573</v>
       </c>
       <c r="P13" t="n">
-        <v>59300</v>
+        <v>2755</v>
       </c>
       <c r="Q13" t="n">
-        <v>22000</v>
+        <v>865</v>
       </c>
       <c r="R13" t="n">
-        <v>-137000</v>
+        <v>-12000</v>
       </c>
       <c r="S13" t="n">
-        <v>-35000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 태양광 관련 긍정적 뉴스 있으나, 전반적인 시장 하락 및 공매도 영향으로 주가 부진.</t>
+          <t>미국 법인 하이브리드 부품 수주(1000억 규모) 및 역대급 3분기 실적 발표. 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['태양광', '공매도', '시장 하락']</t>
+          <t>['하이브리드 부품', '수주', '실적']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1594</v>
+        <v>31150</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-8.81%</t>
+          <t>'-8.25%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="F14" t="n">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="G14" t="n">
-        <v>310</v>
+        <v>182</v>
       </c>
       <c r="H14" t="n">
-        <v>1.77</v>
+        <v>12.79</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1748</v>
+        <v>33950</v>
       </c>
       <c r="K14" t="n">
-        <v>1706</v>
+        <v>33250</v>
       </c>
       <c r="L14" t="n">
-        <v>1895</v>
+        <v>34150</v>
       </c>
       <c r="M14" t="n">
-        <v>1585</v>
+        <v>31100</v>
       </c>
       <c r="N14" t="n">
-        <v>0.83</v>
+        <v>12.81</v>
       </c>
       <c r="O14" t="n">
-        <v>68229877135</v>
+        <v>52770235875</v>
       </c>
       <c r="P14" t="n">
-        <v>2970</v>
+        <v>59300</v>
       </c>
       <c r="Q14" t="n">
-        <v>890</v>
+        <v>22000</v>
       </c>
       <c r="R14" t="n">
-        <v>-457000</v>
+        <v>-137000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-35000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>스페이스X 관련 호재 공시 및 기술력 입증으로 인한 강한 상승 기대감 형성. 2연상 이상 가능성 언급.</t>
+          <t>미국 태양광 관련 긍정적 뉴스 있으나, 전반적인 시장 하락 및 공매도 영향으로 주가 부진.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['스페이스X', '호재공시', '강관']</t>
+          <t>['태양광', '공매도', '시장 하락']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8590</v>
+        <v>1589</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-11.63%</t>
+          <t>'-9.10%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>120</v>
+        <v>186</v>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="G15" t="n">
-        <v>261</v>
+        <v>314</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>1.77</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,47 +1791,47 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>9720</v>
+        <v>1748</v>
       </c>
       <c r="K15" t="n">
-        <v>9930</v>
+        <v>1706</v>
       </c>
       <c r="L15" t="n">
-        <v>9930</v>
+        <v>1895</v>
       </c>
       <c r="M15" t="n">
-        <v>8550</v>
+        <v>1577</v>
       </c>
       <c r="N15" t="n">
-        <v>6.15</v>
+        <v>0.83</v>
       </c>
       <c r="O15" t="n">
-        <v>15157412555</v>
+        <v>69361750461</v>
       </c>
       <c r="P15" t="n">
-        <v>14940</v>
+        <v>2970</v>
       </c>
       <c r="Q15" t="n">
-        <v>5390</v>
+        <v>890</v>
       </c>
       <c r="R15" t="n">
-        <v>-273000</v>
+        <v>-457000</v>
       </c>
       <c r="S15" t="n">
-        <v>-244000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주주환원 미흡 및 중복 상장 우려 제기로 인한 주가 하락세 지속. 개인 투자자들의 불만 및 매도 압력.</t>
+          <t>스페이스X 관련 호재 공시로 인한 급등세 및 2연상 기대감 형성. 거래량 분석 통한 개인 투자자 이탈 가능성 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주주환원', '중복상장', '매도']</t>
+          <t>['스페이스X', '호재 공시', '거래량']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1844,178 +1844,178 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7900</v>
+        <v>8690</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-11.63%</t>
+          <t>'-10.60%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="F16" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="G16" t="n">
-        <v>124</v>
+        <v>298</v>
       </c>
       <c r="H16" t="n">
-        <v>36.01</v>
+        <v>6</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8940</v>
+        <v>9720</v>
       </c>
       <c r="K16" t="n">
-        <v>9000</v>
+        <v>9930</v>
       </c>
       <c r="L16" t="n">
-        <v>9010</v>
+        <v>9930</v>
       </c>
       <c r="M16" t="n">
-        <v>7750</v>
+        <v>8510</v>
       </c>
       <c r="N16" t="n">
-        <v>36.39</v>
+        <v>6.15</v>
       </c>
       <c r="O16" t="n">
-        <v>16497682170</v>
+        <v>16491038610</v>
       </c>
       <c r="P16" t="n">
-        <v>19150</v>
+        <v>14940</v>
       </c>
       <c r="Q16" t="n">
-        <v>3570</v>
+        <v>5390</v>
       </c>
       <c r="R16" t="n">
-        <v>-36000</v>
+        <v>-273000</v>
       </c>
       <c r="S16" t="n">
-        <v>-8000</v>
+        <v>-244000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
+          <t>주주환원 정책 부재 및 중복상장 우려 제기. 단기적인 주가 변동성에 대한 의구심과 매도 의견 혼재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적', '유상증자', 'RCPS']</t>
+          <t>['주주환원', '중복상장', '주가 변동성']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>72300</v>
+        <v>7850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-11.83%</t>
+          <t>'-12.19%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.06</v>
+        <v>-0.38</v>
       </c>
       <c r="E17" t="n">
-        <v>195</v>
+        <v>65</v>
       </c>
       <c r="F17" t="n">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="G17" t="n">
-        <v>645</v>
+        <v>147</v>
       </c>
       <c r="H17" t="n">
-        <v>9.380000000000001</v>
+        <v>36.01</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>82000</v>
+        <v>8940</v>
       </c>
       <c r="K17" t="n">
-        <v>79400</v>
+        <v>9000</v>
       </c>
       <c r="L17" t="n">
-        <v>79400</v>
+        <v>9010</v>
       </c>
       <c r="M17" t="n">
-        <v>70300</v>
+        <v>7750</v>
       </c>
       <c r="N17" t="n">
-        <v>9.44</v>
+        <v>36.39</v>
       </c>
       <c r="O17" t="n">
-        <v>88472035650</v>
+        <v>17148510330</v>
       </c>
       <c r="P17" t="n">
-        <v>184000</v>
+        <v>19150</v>
       </c>
       <c r="Q17" t="n">
-        <v>44750</v>
+        <v>3570</v>
       </c>
       <c r="R17" t="n">
-        <v>-480000</v>
+        <v>-36000</v>
       </c>
       <c r="S17" t="n">
-        <v>-49000</v>
+        <v>-8000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>공매도에 대한 강한 불만과 함께 주가 하락의 이유를 찾기 어렵다는 의견이 제기된다. 금감원 신고 등 적극적인 대응을 주장하는 목소리도 있다.</t>
+          <t>창사 이래 최대 실적 발표에도 주가 하락 지속. 유상증자 및 RCPS 조달 조건에 대한 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공매도', '주가 하락', '금감원']</t>
+          <t>['실적', '유상증자', 'RCPS']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,10 +2023,102 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>033790</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>71300</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>'-13.05%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E18" t="n">
+        <v>207</v>
+      </c>
+      <c r="F18" t="n">
+        <v>117</v>
+      </c>
+      <c r="G18" t="n">
+        <v>690</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>82000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>79400</v>
+      </c>
+      <c r="L18" t="n">
+        <v>79400</v>
+      </c>
+      <c r="M18" t="n">
+        <v>70300</v>
+      </c>
+      <c r="N18" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="O18" t="n">
+        <v>95346542000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>44750</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-480000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-49000</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>공매도 물량 증가 및 주가 급락에 대한 불만 표출. 정치적 이슈와 연관 지어 비판하는 의견 다수.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['공매도', '주가 급락', '정치적 이슈']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>272210</t>
         </is>
